--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,52 +902,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149431</v>
+        <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Eta-Apua, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870376</v>
+        <v>870349</v>
       </c>
       <c r="R4" t="n">
-        <v>7438343</v>
+        <v>7437648</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,49 +987,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121149431</t>
+          <t>https://artportalen.se/Sighting/136857645</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149428</v>
+        <v>121149431</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870199</v>
+        <v>870376</v>
       </c>
       <c r="R5" t="n">
-        <v>7438089</v>
+        <v>7438343</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1118,16 +1109,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121149428</t>
+          <t>https://artportalen.se/Sighting/121149431</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017327</v>
+        <v>136857622</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,41 +1126,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Eta-Apua, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870547</v>
+        <v>870115</v>
       </c>
       <c r="R6" t="n">
-        <v>7437594</v>
+        <v>7438299</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,17 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,27 +1200,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126017327</t>
+          <t>https://artportalen.se/Sighting/136857622</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126017328</v>
+        <v>136857626</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,41 +1228,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aapua, Nb</t>
+          <t>Eta-Apua, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870466</v>
+        <v>870357</v>
       </c>
       <c r="R7" t="n">
-        <v>7437711</v>
+        <v>7438074</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,17 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,18 +1302,2416 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136857626</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136857628</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>870373</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7437887</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857628</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136857630</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>870238</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7437805</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hacksprår</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857630</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136857689</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>870280</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7438296</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857689</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136857618</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>870097</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7438106</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppflog tjäderhöna</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857618</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136857634</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>870398</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7437736</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857634</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136857636</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>870235</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7437811</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857636</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121149428</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Aapua, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>870199</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7438089</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149428</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126017327</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Aapua, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>870547</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7437594</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017327</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126017328</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Aapua, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>870466</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7437711</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126017328</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136857647</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>870308</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7438289</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857647</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136857649</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>870366</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7437970</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857649</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136857651</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>870391</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7437701</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857651</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136857653</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>870317</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7437652</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857653</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136857655</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>870348</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7437637</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857655</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136857657</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>870335</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7437724</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857657</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136857659</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>870317</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7437774</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857659</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136857661</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>870241</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7437830</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857661</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136857664</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>870260</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7437890</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857664</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136857666</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>870268</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7438024</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857666</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136857669</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>870246</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7438008</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857669</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136857671</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>870191</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7438002</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857671</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136857673</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>870190</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7438030</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Större område</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857673</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136857632</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98221</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Eta-Apua, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>870353</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7438066</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857632</t>
         </is>
       </c>
     </row>
@@ -1352,6 +3723,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136857622</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136857626</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136857628</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136857630</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136857689</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136857618</v>
       </c>
       <c r="B11" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>136857634</v>
       </c>
       <c r="B12" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136857636</v>
       </c>
       <c r="B13" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136857622</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136857626</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136857628</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136857630</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136857689</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136857618</v>
       </c>
       <c r="B11" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>136857634</v>
       </c>
       <c r="B12" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136857636</v>
       </c>
       <c r="B13" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136857622</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136857626</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136857628</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136857630</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136857689</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136857618</v>
       </c>
       <c r="B11" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>136857634</v>
       </c>
       <c r="B12" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136857636</v>
       </c>
       <c r="B13" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136857622</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136857626</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136857628</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136857630</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136857689</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>136857618</v>
       </c>
       <c r="B11" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>136857634</v>
       </c>
       <c r="B12" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>136857636</v>
       </c>
       <c r="B13" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136857622</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136857626</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136857628</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136857630</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136857689</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/S 1991-2025 artfynd.xlsx
+++ b/artfynd/S 1991-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136857645</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136857647</v>
       </c>
       <c r="B17" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>136857649</v>
       </c>
       <c r="B18" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136857651</v>
       </c>
       <c r="B19" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>136857653</v>
       </c>
       <c r="B20" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>136857655</v>
       </c>
       <c r="B21" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>136857657</v>
       </c>
       <c r="B22" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>136857659</v>
       </c>
       <c r="B23" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>136857661</v>
       </c>
       <c r="B24" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136857664</v>
       </c>
       <c r="B25" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>136857666</v>
       </c>
       <c r="B26" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>136857669</v>
       </c>
       <c r="B27" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>136857671</v>
       </c>
       <c r="B28" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>136857673</v>
       </c>
       <c r="B29" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>136857632</v>
       </c>
       <c r="B30" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
